--- a/agents/cleaning/agent3-community-intelligence/inputs/cleaned_data.xlsx
+++ b/agents/cleaning/agent3-community-intelligence/inputs/cleaned_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="108">
   <si>
     <t>user_id</t>
   </si>
@@ -55,6 +55,9 @@
     <t>Hello</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>Alice Smith</t>
   </si>
   <si>
@@ -145,6 +148,9 @@
     <t>Meet</t>
   </si>
   <si>
+    <t>Harsh</t>
+  </si>
+  <si>
     <t>5-10 Hours</t>
   </si>
   <si>
@@ -157,6 +163,9 @@
     <t>Ok</t>
   </si>
   <si>
+    <t>Initial</t>
+  </si>
+  <si>
     <t>Data Science</t>
   </si>
   <si>
@@ -277,10 +286,16 @@
     <t>Utf Challenges</t>
   </si>
   <si>
+    <t>Real World</t>
+  </si>
+  <si>
     <t>In A Team</t>
   </si>
   <si>
     <t>Individually</t>
+  </si>
+  <si>
+    <t>Depends In The Project</t>
   </si>
   <si>
     <t>TensorFlow</t>
@@ -680,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -726,28 +741,28 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -758,28 +773,28 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -790,28 +805,28 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -822,28 +837,28 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -854,28 +869,28 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -886,28 +901,28 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -918,28 +933,28 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K8" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -950,28 +965,28 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J9" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -982,28 +997,28 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1014,28 +1029,28 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J11" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K11" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1046,28 +1061,28 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J12" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1078,28 +1093,28 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J13" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1110,28 +1125,28 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I14" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1142,28 +1157,28 @@
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J15" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1174,28 +1189,28 @@
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H16" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J16" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1206,28 +1221,28 @@
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G17" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J17" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K17" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1238,28 +1253,28 @@
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H18" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J18" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1270,28 +1285,28 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H19" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I19" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J19" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1302,28 +1317,28 @@
         <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G20" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H20" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1334,28 +1349,28 @@
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G21" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H21" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J21" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1366,28 +1381,28 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G22" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H22" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J22" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1398,28 +1413,28 @@
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J23" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1430,28 +1445,28 @@
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H24" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J24" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1462,28 +1477,28 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G25" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J25" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1494,28 +1509,28 @@
         <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G26" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H26" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I26" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J26" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1526,28 +1541,28 @@
         <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F27" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G27" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H27" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I27" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J27" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1558,28 +1573,28 @@
         <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G28" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1590,28 +1605,28 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G29" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H29" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I29" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J29" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1622,28 +1637,28 @@
         <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G30" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I30" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J30" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1654,28 +1669,28 @@
         <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G31" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H31" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I31" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J31" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1686,28 +1701,63 @@
         <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H32" t="s">
+        <v>74</v>
+      </c>
+      <c r="J32" t="s">
+        <v>92</v>
+      </c>
+      <c r="K32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33">
+        <v>132</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" t="s">
         <v>46</v>
       </c>
-      <c r="F32" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32" t="s">
-        <v>57</v>
-      </c>
-      <c r="H32" t="s">
-        <v>71</v>
-      </c>
-      <c r="J32" t="s">
-        <v>88</v>
-      </c>
-      <c r="K32" t="s">
-        <v>94</v>
+      <c r="E33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" t="s">
+        <v>51</v>
+      </c>
+      <c r="G33" t="s">
+        <v>62</v>
+      </c>
+      <c r="H33" t="s">
+        <v>74</v>
+      </c>
+      <c r="I33" t="s">
+        <v>90</v>
+      </c>
+      <c r="J33" t="s">
+        <v>93</v>
+      </c>
+      <c r="K33" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
